--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/segregation_of_duties.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/segregation_of_duties.xlsx
@@ -484,12 +484,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Mitigated</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Create vendor + pay</t>
+          <t>Admin + user</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Mitigated</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Create vendor + pay</t>
+          <t>Trade + settle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -567,17 +567,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Post + approve JE</t>
+          <t>Create vendor + pay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -589,17 +589,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Admin + user</t>
+          <t>Trade + settle</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trade + settle</t>
+          <t>Create vendor + pay</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Admin + user</t>
+          <t>Create vendor + pay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Admin + user</t>
+          <t>Post + approve JE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Admin + user</t>
+          <t>Trade + settle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Admin + user</t>
+          <t>Trade + settle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Mitigated</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -743,17 +743,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Create vendor + pay</t>
+          <t>Post + approve JE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mitigated</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trade + settle</t>
+          <t>Admin + user</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Mitigated</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trade + settle</t>
+          <t>Post + approve JE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mitigated</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Admin + user</t>
+          <t>Trade + settle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mitigated</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Post + approve JE</t>
+          <t>Admin + user</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Create vendor + pay</t>
+          <t>Admin + user</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trade + settle</t>
+          <t>Post + approve JE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -897,17 +897,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trade + settle</t>
+          <t>Create vendor + pay</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -919,17 +919,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Admin + user</t>
+          <t>Post + approve JE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -941,17 +941,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trade + settle</t>
+          <t>Admin + user</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Mitigated</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -963,17 +963,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trade + settle</t>
+          <t>Admin + user</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Mitigated</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Post + approve JE</t>
+          <t>Create vendor + pay</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
